--- a/data_processed/results_XGB_kg_CO2e_per_capitaincome.xlsx
+++ b/data_processed/results_XGB_kg_CO2e_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.8108" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.6813" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>609.322265625</v>
+        <v>576.3812866210938</v>
       </c>
       <c r="D2" t="n">
-        <v>28.79414367675781</v>
+        <v>24.16563415527344</v>
       </c>
     </row>
     <row r="3">
@@ -467,14 +467,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>105.4452972412109</v>
+        <v>174.6271667480469</v>
       </c>
       <c r="D3" t="n">
-        <v>4.982924938201904</v>
+        <v>7.3215012550354</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>197.9819030761719</v>
+        <v>321.215087890625</v>
       </c>
       <c r="D4" t="n">
-        <v>9.355835914611816</v>
+        <v>13.46741485595703</v>
       </c>
     </row>
     <row r="5">
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>406.5337219238281</v>
+        <v>215.5031280517578</v>
       </c>
       <c r="D5" t="n">
-        <v>19.2111644744873</v>
+        <v>9.035285949707031</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>distance_train</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>121.0080108642578</v>
+        <v>162.0748291015625</v>
       </c>
       <c r="D6" t="n">
-        <v>5.718356609344482</v>
+        <v>6.795225620269775</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>62.23101043701172</v>
+        <v>320.1093444824219</v>
       </c>
       <c r="D7" t="n">
-        <v>2.940789699554443</v>
+        <v>13.42105484008789</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_train</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>352.4262390136719</v>
+        <v>125.7554473876953</v>
       </c>
       <c r="D8" t="n">
-        <v>16.65426063537598</v>
+        <v>5.272482395172119</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>213.7144470214844</v>
+        <v>97.97378540039062</v>
       </c>
       <c r="D9" t="n">
-        <v>10.09929370880127</v>
+        <v>4.107695579528809</v>
       </c>
     </row>
     <row r="10">
@@ -579,14 +579,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cars_per_adult</t>
+          <t>districtheating_pc</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>47.46974563598633</v>
+        <v>51.6327018737793</v>
       </c>
       <c r="D10" t="n">
-        <v>2.243231296539307</v>
+        <v>2.164777040481567</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>heatpump_pc</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>41.93342208862305</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.758120536804199</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>solarcapacity</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>297.9214172363281</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12.49079418182373</v>
       </c>
     </row>
   </sheetData>
